--- a/resources/table/enum.class.xlsx
+++ b/resources/table/enum.class.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cshyeon\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D89D4D6-8018-4AAF-962A-ADC4808FC02D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3A745F-78CB-4238-8613-545D87DF188A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17790" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="CLASS" sheetId="1" r:id="rId1"/>
@@ -27,23 +27,23 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>NONE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>WARRIOR</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>THIEF</t>
+    <t>ROGUE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MAGICION</t>
+    <t>POET</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ASCETIC</t>
+    <t>MAGE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NONE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -444,7 +444,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1">
         <v>0</v>
@@ -452,7 +452,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -460,7 +460,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -476,7 +476,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5">
         <v>4</v>
